--- a/data/file_generation/reference/data_223/店铺询盘转化趋势-1212_final_res.xlsx
+++ b/data/file_generation/reference/data_223/店铺询盘转化趋势-1212_final_res.xlsx
@@ -28842,20 +28842,28 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83157615-4ACC-409E-9143-65D7945FA2D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE5F3A64-A971-4B7E-B0FD-692F341881D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7DDF54-B5E7-47D1-8E97-F01F861E8D7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711B08A3-03E2-42F5-A819-E02462CDD3C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{183CDE54-D024-4ADB-A75E-16FDC14AF2E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A3B8D2-17EA-4448-9A31-7542A3ED52D8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
